--- a/data/trans_orig/RUIDO_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45963</t>
+          <t>45964</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57161</t>
+          <t>57754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83284</t>
+          <t>84283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101371</t>
+          <t>101687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>27981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43095</t>
+          <t>42096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57764</t>
+          <t>57646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71509</t>
+          <t>71294</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88455</t>
+          <t>88151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111903</t>
+          <t>111859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153908</t>
+          <t>153660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180210</t>
+          <t>179765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23704</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47152</t>
+          <t>47456</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43183</t>
+          <t>43628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69485</t>
+          <t>69733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65834</t>
+          <t>66002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90361</t>
+          <t>91424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54553</t>
+          <t>53666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70728</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126292</t>
+          <t>127103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158401</t>
+          <t>159926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34084</t>
+          <t>33916</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18644</t>
+          <t>18773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34819</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>29364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62998</t>
+          <t>62187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64085</t>
+          <t>64517</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76560</t>
+          <t>77109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62433</t>
+          <t>62735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77213</t>
+          <t>77019</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131195</t>
+          <t>132366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150898</t>
+          <t>151428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12420</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27217</t>
+          <t>26915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27732</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47435</t>
+          <t>46264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>240776</t>
+          <t>242664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274374</t>
+          <t>275054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>268712</t>
+          <t>268513</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>523082</t>
+          <t>519201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>570088</t>
+          <t>569331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57169</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90767</t>
+          <t>88879</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82610</t>
+          <t>82705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117437</t>
+          <t>117636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147603</t>
+          <t>148360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194609</t>
+          <t>198490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49090</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41513</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>55763</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>41903</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36589</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45964</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51361</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43539</t>
+          <t>37097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57754</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>93263</t>
+          <t>91356</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84283</t>
+          <t>82285</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101687</t>
+          <t>99615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19041</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12368</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26618</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12956</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8895</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18270</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>23,62%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27981</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>33116</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>24085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42096</t>
+          <t>41415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>96518</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83020</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>103942</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>65,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>65219</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>57646</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>71294</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>74,29%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>81,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>103469</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88151</t>
+          <t>57170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111859</t>
+          <t>71528</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>168688</t>
+          <t>161203</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153660</t>
+          <t>147782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179765</t>
+          <t>172316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29516</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22092</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43014</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>22567</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16492</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30140</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47456</t>
+          <t>29578</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>54705</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43628</t>
+          <t>40466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69733</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135607</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135607</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>135607</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54545</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46759</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61580</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>78201</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>66002</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>91424</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>49240</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53666</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70599</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>140782</t>
+          <t>103785</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127103</t>
+          <t>93304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159926</t>
+          <t>113623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25724</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18689</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33510</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21717</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8494</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33916</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26791</t>
+          <t>22326</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18773</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>48050</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29364</t>
+          <t>38212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62187</t>
+          <t>58531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89372</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89372</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89372</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>66457</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>59764</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>72345</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>79,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>71,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>86,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>71354</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>64517</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>77109</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>80,19%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>86,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70883</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62735</t>
+          <t>61544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77019</t>
+          <t>74330</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>142237</t>
+          <t>134949</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132366</t>
+          <t>125187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151428</t>
+          <t>143543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17073</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11185</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23766</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>28,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>17626</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11871</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24463</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26915</t>
+          <t>25342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36393</t>
+          <t>35467</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>26873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46264</t>
+          <t>45229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>86886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>86886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>86886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>266611</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>249873</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>282316</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>351</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>256677</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>242664</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>275054</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>82,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224681</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>211785</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>236506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>544970</t>
+          <t>491292</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>519201</t>
+          <t>469918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>569331</t>
+          <t>509658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>91354</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75649</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>108092</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>74866</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>56489</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>88879</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>97855</t>
+          <t>76088</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82705</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117636</t>
+          <t>88984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>172721</t>
+          <t>167441</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148360</t>
+          <t>149075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198490</t>
+          <t>188815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
